--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FD8FF0-4D90-4551-A819-2AA7B1EA1058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFC8861-6193-4889-AD21-6332EFBBFC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>材料名称</t>
   </si>
@@ -491,13 +491,28 @@
   </si>
   <si>
     <t>猫咪水盆</t>
+  </si>
+  <si>
+    <t>硝酸钾</t>
+  </si>
+  <si>
+    <t>小型火焰精华</t>
+  </si>
+  <si>
+    <t>大型火焰精华</t>
+  </si>
+  <si>
+    <t>火焰精华</t>
+  </si>
+  <si>
+    <t>极好的武器油</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -520,6 +535,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -563,7 +585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -577,12 +599,22 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0070C0"/>
+      <color rgb="FF7030A0"/>
+      <color rgb="FFFFC000"/>
+      <color rgb="FFFFFFFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -879,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B172"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1813,61 +1845,29 @@
       <c r="B153" s="3"/>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A154" s="7"/>
+      <c r="A154" s="7" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A155" s="7"/>
+      <c r="A155" s="10" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A156" s="7"/>
+      <c r="A156" s="9" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A157" s="7"/>
+      <c r="A157" s="8" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A158" s="7"/>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A159" s="7"/>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A160" s="7"/>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A161" s="7"/>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A162" s="7"/>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A163" s="7"/>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A164" s="7"/>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A165" s="7"/>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A166" s="7"/>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A167" s="7"/>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A168" s="7"/>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A169" s="7"/>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A170" s="7"/>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A171" s="7"/>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A172" s="7"/>
+      <c r="A158" s="10" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFC8861-6193-4889-AD21-6332EFBBFC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4E481C-0BC8-4938-A737-DF7FF19D2A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t>材料名称</t>
   </si>
@@ -506,6 +506,18 @@
   </si>
   <si>
     <t>极好的武器油</t>
+  </si>
+  <si>
+    <t>山毛榉</t>
+  </si>
+  <si>
+    <t>岩盐</t>
+  </si>
+  <si>
+    <t>对流亡者而言，一袋盐的价值比得上一袋金子</t>
+  </si>
+  <si>
+    <t>不需要魔法就能确保带来火热的火焰！可作为燃料使用</t>
   </si>
 </sst>
 </file>
@@ -607,14 +619,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FF0070C0"/>
-      <color rgb="FF7030A0"/>
-      <color rgb="FFFFC000"/>
-      <color rgb="FFFFFFFF"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -911,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B158"/>
+  <dimension ref="A1:B174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1869,6 +1873,64 @@
         <v>161</v>
       </c>
     </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A159" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A160" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A161" s="7"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A162" s="7"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A172" s="7"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A174" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4E481C-0BC8-4938-A737-DF7FF19D2A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C147E6-0FE9-43F5-AE89-ADBF592F2337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,10 +514,10 @@
     <t>岩盐</t>
   </si>
   <si>
-    <t>对流亡者而言，一袋盐的价值比得上一袋金子</t>
-  </si>
-  <si>
     <t>不需要魔法就能确保带来火热的火焰！可作为燃料使用</t>
+  </si>
+  <si>
+    <t>对流亡者而言，一袋盐的价值比得上一袋金子。可在以下地点获取：被诅咒的天文台/商人护送/破损大车/维比约恩的巢穴</t>
   </si>
 </sst>
 </file>
@@ -597,7 +597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -613,6 +613,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1878,15 +1881,15 @@
         <v>162</v>
       </c>
       <c r="B159" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A160" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B160" t="s">
-        <v>164</v>
+      <c r="B160" s="11" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.45">

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C147E6-0FE9-43F5-AE89-ADBF592F2337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C290000E-71C8-43F2-AEA5-6AE09AB7A529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <si>
     <t>材料名称</t>
   </si>
@@ -517,7 +517,31 @@
     <t>不需要魔法就能确保带来火热的火焰！可作为燃料使用</t>
   </si>
   <si>
-    <t>对流亡者而言，一袋盐的价值比得上一袋金子。可在以下地点获取：被诅咒的天文台/商人护送/破损大车/维比约恩的巢穴</t>
+    <t>专为刨平木材而造的工具，前提是你会用。是二级木工台的组装材料。</t>
+  </si>
+  <si>
+    <t>掉落地点</t>
+  </si>
+  <si>
+    <t>被诅咒的天文台/商人护送/破损大车/维比约恩的巢穴</t>
+  </si>
+  <si>
+    <t>对流亡者而言，一袋盐的价值比得上一袋金子</t>
+  </si>
+  <si>
+    <t>商人护送/破损大车/野蛮人营地</t>
+  </si>
+  <si>
+    <t>墓地之夜/死亡村庄</t>
+  </si>
+  <si>
+    <t>商人护送</t>
+  </si>
+  <si>
+    <t>死亡村庄/被咒者的财宝</t>
+  </si>
+  <si>
+    <t>破损大车/野蛮人营地/被咒者财宝</t>
   </si>
 </sst>
 </file>
@@ -597,24 +621,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -918,1021 +959,1203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B174"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="3" max="3" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+      <c r="B12" s="5"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="3"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" s="4" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="4" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="5" t="s">
+      <c r="B24" s="5"/>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" s="4" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="3"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
+      <c r="B26" s="5"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
+      <c r="B29" s="5"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" s="4" t="s">
+      <c r="B30" s="5"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
+      <c r="B32" s="5"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
+      <c r="B33" s="5"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
+      <c r="B34" s="5"/>
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" s="4" t="s">
+      <c r="B35" s="5"/>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" s="4" t="s">
+      <c r="B36" s="5"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" s="4" t="s">
+      <c r="B37" s="5"/>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="3"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" s="5" t="s">
+      <c r="B38" s="5"/>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
+      <c r="B39" s="5"/>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="3"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
+      <c r="B40" s="5"/>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
+      <c r="B41" s="5"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="4"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
+      <c r="B44" s="5"/>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" s="5" t="s">
+      <c r="B45" s="5"/>
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
+      <c r="B47" s="5"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49" s="5" t="s">
+      <c r="B48" s="5"/>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A50" s="4" t="s">
+      <c r="B49" s="5"/>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="3"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
+      <c r="B50" s="5"/>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A52" s="6" t="s">
+      <c r="B51" s="5"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="3"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A53" s="4" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="4"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
+      <c r="B53" s="5"/>
+      <c r="C53" s="4"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="3"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A55" s="6" t="s">
+      <c r="B54" s="5"/>
+      <c r="C54" s="4"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A56" s="4" t="s">
+      <c r="B55" s="5"/>
+      <c r="C55" s="4"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="3"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A57" s="6" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="4"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="3"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
+      <c r="B57" s="5"/>
+      <c r="C57" s="4"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="3"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A59" s="6" t="s">
+      <c r="B58" s="5"/>
+      <c r="C58" s="4"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="3"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
+      <c r="B59" s="5"/>
+      <c r="C59" s="4"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B60" s="3"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
+      <c r="B60" s="5"/>
+      <c r="C60" s="4"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="3"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A62" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="4"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B62" s="3"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A63" s="4" t="s">
+      <c r="B62" s="5"/>
+      <c r="C62" s="4"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="3"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A64" s="4" t="s">
+      <c r="B63" s="5"/>
+      <c r="C63" s="4"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="3"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A65" s="4" t="s">
+      <c r="B64" s="5"/>
+      <c r="C64" s="4"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="3"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
+      <c r="B65" s="5"/>
+      <c r="C65" s="4"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B66" s="3"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
+      <c r="B66" s="5"/>
+      <c r="C66" s="4"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="3"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
+      <c r="B67" s="5"/>
+      <c r="C67" s="4"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="3"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
+      <c r="B68" s="5"/>
+      <c r="C68" s="4"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B69" s="3"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
+      <c r="B69" s="5"/>
+      <c r="C69" s="4"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B70" s="3"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
+      <c r="B70" s="5"/>
+      <c r="C70" s="4"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A71" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B71" s="3"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
+      <c r="B71" s="5"/>
+      <c r="C71" s="4"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A72" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B72" s="3"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
+      <c r="B72" s="5"/>
+      <c r="C72" s="4"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A73" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="3"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
+      <c r="B73" s="5"/>
+      <c r="C73" s="4"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A74" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B74" s="3"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
+      <c r="B74" s="5"/>
+      <c r="C74" s="4"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A75" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="3"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
+      <c r="B75" s="5"/>
+      <c r="C75" s="4"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A76" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B76" s="3"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
+      <c r="B76" s="5"/>
+      <c r="C76" s="4"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A77" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B77" s="3"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A78" s="4" t="s">
+      <c r="B77" s="5"/>
+      <c r="C77" s="4"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A78" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B78" s="3"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A79" s="4" t="s">
+      <c r="B78" s="5"/>
+      <c r="C78" s="4"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A79" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B79" s="3"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
+      <c r="B79" s="5"/>
+      <c r="C79" s="4"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A80" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="3"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
+      <c r="B80" s="5"/>
+      <c r="C80" s="4"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A81" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="3"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A82" s="5" t="s">
+      <c r="B81" s="5"/>
+      <c r="C81" s="4"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A82" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="3"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A83" s="4" t="s">
+      <c r="B82" s="5"/>
+      <c r="C82" s="4"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A83" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B83" s="3"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A84" s="5" t="s">
+      <c r="B83" s="5"/>
+      <c r="C83" s="4"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A84" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B84" s="3"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
+      <c r="B84" s="5"/>
+      <c r="C84" s="4"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A85" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B85" s="3"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A86" s="4" t="s">
+      <c r="B85" s="5"/>
+      <c r="C85" s="4"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A86" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B86" s="3"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A87" s="4" t="s">
+      <c r="B86" s="5"/>
+      <c r="C86" s="4"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A87" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B87" s="3"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
+      <c r="B87" s="5"/>
+      <c r="C87" s="4"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A88" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B88" s="3"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A89" s="4" t="s">
+      <c r="B88" s="5"/>
+      <c r="C88" s="4"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A89" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B89" s="3"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A90" s="4" t="s">
+      <c r="B89" s="5"/>
+      <c r="C89" s="4"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A90" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B90" s="3"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A91" s="5" t="s">
+      <c r="B90" s="5"/>
+      <c r="C90" s="4"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A91" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B91" s="3"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A92" s="6" t="s">
+      <c r="B91" s="5"/>
+      <c r="C91" s="4"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A92" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="3"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A93" s="4" t="s">
+      <c r="B92" s="5"/>
+      <c r="C92" s="4"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A93" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B93" s="3"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A94" s="5" t="s">
+      <c r="B93" s="5"/>
+      <c r="C93" s="4"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A94" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B94" s="3"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A95" s="5" t="s">
+      <c r="B94" s="5"/>
+      <c r="C94" s="4"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A95" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B95" s="3"/>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A96" s="6" t="s">
+      <c r="B95" s="5"/>
+      <c r="C95" s="4"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A96" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B96" s="3"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A97" s="5" t="s">
+      <c r="B96" s="5"/>
+      <c r="C96" s="4"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A97" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B97" s="3"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A98" s="5" t="s">
+      <c r="B97" s="5"/>
+      <c r="C97" s="4"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A98" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B98" s="3"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A99" s="4" t="s">
+      <c r="B98" s="5"/>
+      <c r="C98" s="4"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A99" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B99" s="3"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A100" s="6" t="s">
+      <c r="B99" s="5"/>
+      <c r="C99" s="4"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A100" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B100" s="3"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A101" s="6" t="s">
+      <c r="B100" s="5"/>
+      <c r="C100" s="4"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A101" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B101" s="3"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A102" s="4" t="s">
+      <c r="B101" s="5"/>
+      <c r="C101" s="4"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A102" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B102" s="3"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A103" s="4" t="s">
+      <c r="B102" s="5"/>
+      <c r="C102" s="4"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A103" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B103" s="3"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A104" s="5" t="s">
+      <c r="B103" s="5"/>
+      <c r="C103" s="4"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A104" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B104" s="3"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A105" s="5" t="s">
+      <c r="B104" s="5"/>
+      <c r="C104" s="4"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A105" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B105" s="3"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A106" s="4" t="s">
+      <c r="B105" s="5"/>
+      <c r="C105" s="4"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A106" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B106" s="3"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A107" s="8" t="s">
+      <c r="B106" s="5"/>
+      <c r="C106" s="4"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A107" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B107" s="3"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A108" s="8" t="s">
+      <c r="B107" s="5"/>
+      <c r="C107" s="4"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A108" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B108" s="3"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A109" s="4" t="s">
+      <c r="B108" s="5"/>
+      <c r="C108" s="4"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A109" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B109" s="3"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A110" s="4" t="s">
+      <c r="B109" s="5"/>
+      <c r="C109" s="4"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A110" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B110" s="3"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A111" s="4" t="s">
+      <c r="B110" s="5"/>
+      <c r="C110" s="4"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A111" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B111" s="3"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A112" s="8" t="s">
+      <c r="B111" s="5"/>
+      <c r="C111" s="4"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A112" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B112" s="3"/>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A113" s="4" t="s">
+      <c r="B112" s="5"/>
+      <c r="C112" s="4"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A113" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B113" s="3"/>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A114" s="7" t="s">
+      <c r="B113" s="5"/>
+      <c r="C113" s="4"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A114" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B114" s="3"/>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A115" s="4" t="s">
+      <c r="B114" s="5"/>
+      <c r="C114" s="4"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A115" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B115" s="3"/>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A116" s="8" t="s">
+      <c r="B115" s="5"/>
+      <c r="C115" s="4"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A116" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B116" s="3"/>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A117" s="4" t="s">
+      <c r="B116" s="5"/>
+      <c r="C116" s="4"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A117" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B117" s="3"/>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A118" s="8" t="s">
+      <c r="B117" s="5"/>
+      <c r="C117" s="4"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A118" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B118" s="3"/>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A119" s="8" t="s">
+      <c r="B118" s="5"/>
+      <c r="C118" s="4"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A119" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B119" s="3"/>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A120" s="8" t="s">
+      <c r="B119" s="5"/>
+      <c r="C119" s="4"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A120" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B120" s="3"/>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A121" s="4" t="s">
+      <c r="B120" s="5"/>
+      <c r="C120" s="4"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A121" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B121" s="3"/>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A122" s="7" t="s">
+      <c r="B121" s="5"/>
+      <c r="C121" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A122" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B122" s="3"/>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A123" s="4" t="s">
+      <c r="B122" s="5"/>
+      <c r="C122" s="4"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A123" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B123" s="3"/>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A124" s="7" t="s">
+      <c r="B123" s="5"/>
+      <c r="C123" s="4"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A124" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B124" s="3"/>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A125" s="4" t="s">
+      <c r="B124" s="5"/>
+      <c r="C124" s="4"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A125" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B125" s="3"/>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A126" s="4" t="s">
+      <c r="B125" s="5"/>
+      <c r="C125" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A126" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B126" s="3"/>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A127" s="4" t="s">
+      <c r="B126" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A127" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B127" s="3"/>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A128" s="4" t="s">
+      <c r="B127" s="5"/>
+      <c r="C127" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A128" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B128" s="3"/>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A129" s="6" t="s">
+      <c r="B128" s="5"/>
+      <c r="C128" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A129" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B129" s="3"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A130" s="6" t="s">
+      <c r="B129" s="5"/>
+      <c r="C129" s="4"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A130" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B130" s="3"/>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A131" s="8" t="s">
+      <c r="B130" s="5"/>
+      <c r="C130" s="4"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A131" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B131" s="3"/>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A132" s="4" t="s">
+      <c r="B131" s="5"/>
+      <c r="C131" s="4"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A132" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B132" s="3"/>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A133" s="4" t="s">
+      <c r="B132" s="5"/>
+      <c r="C132" s="4"/>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A133" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B133" s="3"/>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A134" s="6" t="s">
+      <c r="B133" s="5"/>
+      <c r="C133" s="4"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A134" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B134" s="3"/>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A135" s="6" t="s">
+      <c r="B134" s="5"/>
+      <c r="C134" s="4"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A135" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B135" s="3"/>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A136" s="8" t="s">
+      <c r="B135" s="5"/>
+      <c r="C135" s="4"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A136" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B136" s="3"/>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A137" s="7" t="s">
+      <c r="B136" s="5"/>
+      <c r="C136" s="4"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A137" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B137" s="3"/>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A138" s="8" t="s">
+      <c r="B137" s="5"/>
+      <c r="C137" s="4"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A138" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B138" s="3"/>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A139" s="6" t="s">
+      <c r="B138" s="5"/>
+      <c r="C138" s="4"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A139" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B139" s="3"/>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A140" s="7" t="s">
+      <c r="B139" s="5"/>
+      <c r="C139" s="4"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A140" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B140" s="3"/>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A141" s="6" t="s">
+      <c r="B140" s="5"/>
+      <c r="C140" s="4"/>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A141" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B141" s="3"/>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A142" s="7" t="s">
+      <c r="B141" s="5"/>
+      <c r="C141" s="4"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A142" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B142" s="3"/>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A143" s="6" t="s">
+      <c r="B142" s="5"/>
+      <c r="C142" s="4"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A143" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B143" s="3"/>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A144" s="4" t="s">
+      <c r="B143" s="5"/>
+      <c r="C143" s="4"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A144" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B144" s="3"/>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A145" s="4" t="s">
+      <c r="B144" s="5"/>
+      <c r="C144" s="4"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A145" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B145" s="3"/>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A146" s="8" t="s">
+      <c r="B145" s="5"/>
+      <c r="C145" s="4"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A146" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B146" s="3"/>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A147" s="8" t="s">
+      <c r="B146" s="5"/>
+      <c r="C146" s="4"/>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A147" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B147" s="3"/>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A148" s="8" t="s">
+      <c r="B147" s="5"/>
+      <c r="C147" s="4"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A148" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B148" s="3"/>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A149" s="4" t="s">
+      <c r="B148" s="5"/>
+      <c r="C148" s="4"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A149" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B149" s="3"/>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A150" s="4" t="s">
+      <c r="B149" s="5"/>
+      <c r="C149" s="4"/>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A150" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B150" s="3"/>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A151" s="8" t="s">
+      <c r="B150" s="5"/>
+      <c r="C150" s="4"/>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A151" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B151" s="3"/>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A152" s="4" t="s">
+      <c r="B151" s="5"/>
+      <c r="C151" s="4"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A152" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B152" s="3"/>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A153" s="4" t="s">
+      <c r="B152" s="5"/>
+      <c r="C152" s="4"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A153" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B153" s="3"/>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A154" s="7" t="s">
+      <c r="B153" s="5"/>
+      <c r="C153" s="4"/>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A154" s="10" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A155" s="10" t="s">
+      <c r="B154" s="4"/>
+      <c r="C154" s="4"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A155" s="11" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A156" s="9" t="s">
+      <c r="B155" s="4"/>
+      <c r="C155" s="4"/>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A156" s="12" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A157" s="8" t="s">
+      <c r="B156" s="4"/>
+      <c r="C156" s="4"/>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A157" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A158" s="10" t="s">
+      <c r="B157" s="4"/>
+      <c r="C157" s="4"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A158" s="11" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A159" s="10" t="s">
+      <c r="B158" s="4"/>
+      <c r="C158" s="4"/>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A159" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A160" s="10" t="s">
+      <c r="C159" s="4"/>
+    </row>
+    <row r="160" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A160" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B160" s="11" t="s">
-        <v>165</v>
+      <c r="B160" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A161" s="7"/>
+      <c r="A161" s="1"/>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A162" s="7"/>
+      <c r="A162" s="1"/>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A163" s="7"/>
+      <c r="A163" s="1"/>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A164" s="7"/>
+      <c r="A164" s="1"/>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A165" s="7"/>
+      <c r="A165" s="1"/>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A166" s="7"/>
+      <c r="A166" s="1"/>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A167" s="7"/>
+      <c r="A167" s="1"/>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A168" s="7"/>
+      <c r="A168" s="1"/>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A169" s="7"/>
+      <c r="A169" s="1"/>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A170" s="7"/>
+      <c r="A170" s="1"/>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A171" s="7"/>
+      <c r="A171" s="1"/>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A172" s="7"/>
+      <c r="A172" s="1"/>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A173" s="7"/>
+      <c r="A173" s="1"/>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A174" s="7"/>
+      <c r="A174" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C290000E-71C8-43F2-AEA5-6AE09AB7A529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437A8CC0-FC62-469C-89E3-6747BE2E38C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>材料名称</t>
   </si>
@@ -542,6 +542,33 @@
   </si>
   <si>
     <t>破损大车/野蛮人营地/被咒者财宝</t>
+  </si>
+  <si>
+    <t>使用这个铁锭，您可以打制坚固的护甲和头盔，在熔炉中由2个铁矿石烧制而成，或者5个铁碎片烧制而成</t>
+  </si>
+  <si>
+    <t>死亡村庄Lv170-Lv200</t>
+  </si>
+  <si>
+    <t>这种金属可能比较软，但加工方便</t>
+  </si>
+  <si>
+    <t>细绳可以将倍吊死的人的痛苦加倍</t>
+  </si>
+  <si>
+    <t>由未知动物的皮制成的皮革，上面覆盖着神秘的符文</t>
+  </si>
+  <si>
+    <t>险恶城堡/叛徒地下墓穴/3-5级图/死灵法师的巢穴</t>
+  </si>
+  <si>
+    <t>这些烂布片可以被缝制在一起，制成更结实的布料</t>
+  </si>
+  <si>
+    <t>它其实比看起来更结实</t>
+  </si>
+  <si>
+    <t>酷吏地下城/1-5级图/荒废墓穴</t>
   </si>
 </sst>
 </file>
@@ -1005,47 +1032,65 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="4"/>
+      <c r="B5" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="4"/>
+      <c r="B8" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>180</v>
+      </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437A8CC0-FC62-469C-89E3-6747BE2E38C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6404E1E6-A3D5-4E2E-BBA1-7879229972E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,9 +523,6 @@
     <t>掉落地点</t>
   </si>
   <si>
-    <t>被诅咒的天文台/商人护送/破损大车/维比约恩的巢穴</t>
-  </si>
-  <si>
     <t>对流亡者而言，一袋盐的价值比得上一袋金子</t>
   </si>
   <si>
@@ -569,6 +566,9 @@
   </si>
   <si>
     <t>酷吏地下城/1-5级图/荒废墓穴</t>
+  </si>
+  <si>
+    <t>被诅咒的天文台/商人护送/破损大车/维比约恩的巢穴/中尉咸味</t>
   </si>
 </sst>
 </file>
@@ -1037,10 +1037,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -1048,7 +1048,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C6" s="4"/>
     </row>
@@ -1057,7 +1057,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C7" s="4"/>
     </row>
@@ -1066,10 +1066,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C9" s="4"/>
     </row>
@@ -1086,10 +1086,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.45">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.45">
@@ -1909,7 +1909,7 @@
         <v>165</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.45">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.45">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.45">
@@ -2154,10 +2154,10 @@
         <v>163</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.45">
